--- a/results/final_20260514_v2_summary/Yeast_BinaryVector_summary.xlsx
+++ b/results/final_20260514_v2_summary/Yeast_BinaryVector_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE12"/>
+  <dimension ref="A1:BE14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3869,6 +3869,580 @@
       <c r="BE12" t="inlineStr">
         <is>
           <t>0.0761±0.0131</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ecc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.7491±0.0162</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.7792±0.0171</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.7800±0.0146</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.7325±0.0171</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.7316±0.0056</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.7369±0.0083</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.7283±0.0101</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.6949±0.0105</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.5990±0.0169</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.5715±0.0170</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.5598±0.0128</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.5645±0.0160</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.6260±0.0089</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.6117±0.0094</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.6034±0.0075</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.5934±0.0095</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0.8126±0.0043</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.8088±0.0042</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0.8042±0.0037</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>0.7920±0.0049</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0.5270±0.0100</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.5076±0.0109</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.4960±0.0076</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0.4796±0.0100</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.3726±0.0081</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.3524±0.0091</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.3468±0.0102</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.3543±0.0104</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.6421±0.0706</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>0.6219±0.0549</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>0.6000±0.0534</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.5097±0.0401</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.3483±0.0109</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>0.3247±0.0119</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>0.3183±0.0098</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.3301±0.0112</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>0.9998±0.0006</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>0.9992±0.0014</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0.6562±0.0086</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0.6413±0.0089</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.6319±0.0066</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>0.6194±0.0078</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>0.7376±0.0075</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>0.7419±0.0089</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>0.7331±0.0097</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>0.6945±0.0135</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>0.5913±0.0173</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>0.5651±0.0167</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>0.5554±0.0127</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>0.5593±0.0143</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>0.2201±0.0215</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>0.1813±0.0190</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.1508±0.0161</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.1137±0.0172</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mlknn</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.6516±0.0127</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.6147±0.0236</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.5376±0.0294</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.4262±0.0424</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.6882±0.0071</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.6647±0.0119</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.6100±0.0158</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.5143±0.0222</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.5970±0.0071</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.5830±0.0191</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.5725±0.0210</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.5445±0.0268</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.6117±0.0083</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.5927±0.0140</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.5615±0.0112</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.4998±0.0184</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0.7997±0.0043</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.7856±0.0048</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0.7571±0.0074</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0.6998±0.0124</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0.5111±0.0102</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.4853±0.0149</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.4432±0.0101</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.3709±0.0176</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.4127±0.0067</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.4061±0.0089</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.4055±0.0108</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.3858±0.0089</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.5766±0.0417</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0.4927±0.0232</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.4458±0.0232</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0.3879±0.0121</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.3810±0.0026</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>0.3808±0.0122</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>0.3960±0.0192</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.4107±0.0216</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>0.9989±0.0027</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>0.9710±0.0334</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>0.8657±0.0738</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>0.6420±0.0058</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.6207±0.0114</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.5860±0.0086</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>0.5213±0.0168</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.6990±0.0028</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.6681±0.0117</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.6061±0.0177</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>0.5044±0.0202</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>0.5937±0.0091</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0.5801±0.0198</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.5682±0.0210</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>0.5404±0.0262</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.1978±0.0204</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>0.1533±0.0179</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.0866±0.0126</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.0231±0.0111</t>
         </is>
       </c>
     </row>
